--- a/cp-short-description/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-short-description/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:20:15+00:00</t>
+    <t>2026-06-25T15:53:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1207,7 +1207,7 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Commentaire associé au document.</t>
+    <t>Description du document source, lisible par l'homme correspondant au commentaire associé au document</t>
   </si>
   <si>
     <t>Human-readable description of the source document.</t>

--- a/cp-short-description/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-short-description/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:53:08+00:00</t>
+    <t>2026-06-25T16:02:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1207,7 +1207,7 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Description du document source, lisible par l'homme correspondant au commentaire associé au document</t>
+    <t>Description du document source, lisible par l'homme, correspondant au commentaire associé au document</t>
   </si>
   <si>
     <t>Human-readable description of the source document.</t>
